--- a/docs/inshi/inshi-table.xlsx
+++ b/docs/inshi/inshi-table.xlsx
@@ -382,22 +382,23 @@
     <mergeCell ref="A5:C5"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C7" r:id="rId7"/>
-    <hyperlink ref="C8" r:id="rId8"/>
-    <hyperlink ref="C9" r:id="rId9"/>
-    <hyperlink ref="C10" r:id="rId10"/>
-    <hyperlink ref="C11" r:id="rId11"/>
-    <hyperlink ref="C12" r:id="rId12"/>
-    <hyperlink ref="C13" r:id="rId13"/>
-    <hyperlink ref="C14" r:id="rId14"/>
-    <hyperlink ref="C15" r:id="rId15"/>
-    <hyperlink ref="C16" r:id="rId16"/>
-    <hyperlink ref="C17" r:id="rId17"/>
-    <hyperlink ref="C18" r:id="rId18"/>
-    <hyperlink ref="C19" r:id="rId19"/>
-    <hyperlink ref="C20" r:id="rId20"/>
-    <hyperlink ref="C21" r:id="rId21"/>
-    <hyperlink ref="C22" r:id="rId22"/>
+    <hyperlink ref="A4" r:id="rId1"/>
+    <hyperlink ref="C7" r:id="rId2"/>
+    <hyperlink ref="C8" r:id="rId3"/>
+    <hyperlink ref="C9" r:id="rId4"/>
+    <hyperlink ref="C10" r:id="rId5"/>
+    <hyperlink ref="C11" r:id="rId6"/>
+    <hyperlink ref="C12" r:id="rId7"/>
+    <hyperlink ref="C13" r:id="rId8"/>
+    <hyperlink ref="C14" r:id="rId9"/>
+    <hyperlink ref="C15" r:id="rId10"/>
+    <hyperlink ref="C16" r:id="rId11"/>
+    <hyperlink ref="C17" r:id="rId12"/>
+    <hyperlink ref="C18" r:id="rId13"/>
+    <hyperlink ref="C19" r:id="rId14"/>
+    <hyperlink ref="C20" r:id="rId15"/>
+    <hyperlink ref="C21" r:id="rId16"/>
+    <hyperlink ref="C22" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="2"/>
